--- a/outputs/45300.xlsx
+++ b/outputs/45300.xlsx
@@ -126,12 +126,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -327,42 +331,42 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="93.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="93.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="str">
-        <f aca="false">LEFT(A1, FIND("FT", A1)-1)</f>
+      <c r="B1" s="1" t="str">
+        <f aca="false">LEFT(A1,FIND("FT",A1)-1)</f>
         <v>Transfer 27976614 KHALIL MORTEZA BAGHESTANI TAJALI </v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="str">
-        <f aca="false">LEFT(A2, FIND("FT", A2)-1)</f>
+      <c r="B2" s="1" t="str">
+        <f aca="false">LEFT(A2,FIND("FT",A2)-1)</f>
         <v>Transfer 29419550 HAMED ABBASI POUR SHAMSOLLAH </v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="str">
-        <f aca="false">LEFT(A3, FIND("FT", A3)-1)</f>
+      <c r="B3" s="1" t="str">
+        <f aca="false">LEFT(A3,FIND("FT",A3)-1)</f>
         <v>Transfer 27575850 HAITHAM AL RAWA </v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="str">
-        <f aca="false">LEFT(A4, FIND("FT", A4)-1)</f>
+      <c r="B4" s="1" t="str">
+        <f aca="false">LEFT(A4,FIND("FT",A4)-1)</f>
         <v>Transfer 29935127 SREELATHA RAMACHANDRAN </v>
       </c>
     </row>
